--- a/cbreader2X/nav/advance_nav.xlsx
+++ b/cbreader2X/nav/advance_nav.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607ACFDE-14AE-4675-A005-F144F8EFA6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E86AC4-2855-44AE-A90B-C29081ED420F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12252" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4758" uniqueCount="4621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4771" uniqueCount="4634">
   <si>
     <t>歷代藏經補輯</t>
   </si>
@@ -14624,12 +14624,62 @@
     <t>YP0010 勝鬘師子吼一乘大方便方廣經講記</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>YP0012 解深密經語體釋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0011 維摩詰所說經講記（上）（下）(第1卷-第6卷)(第7卷-第6卷)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0014 華嚴經普賢行願品講記</t>
+  </si>
+  <si>
+    <t>YP0013 佛說彌勒大成佛經講記</t>
+  </si>
+  <si>
+    <t>YP0015 觀世音菩薩普門品講記</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0016 藥師經講記</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0017 六祖壇經講記</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0018 梵網經菩薩戒本講記</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>律釋篇</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0019 毘尼日用切要講記</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0020 八關齋戒十講</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>論釋篇</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0021 異部宗輪論語體釋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14715,6 +14765,13 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -14736,7 +14793,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -14752,6 +14809,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15034,7 +15094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4750"/>
+  <dimension ref="A1:F4763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="43.625" style="1" customWidth="1"/>
@@ -38840,84 +38900,162 @@
         <v>4613</v>
       </c>
     </row>
-    <row r="4737" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4737" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C4737" s="3"/>
       <c r="D4737" s="3" t="s">
         <v>4614</v>
       </c>
     </row>
-    <row r="4738" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4738" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C4738" s="3"/>
       <c r="D4738" s="3" t="s">
         <v>4615</v>
       </c>
     </row>
-    <row r="4739" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4739" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C4739" s="3"/>
       <c r="D4739" s="3" t="s">
         <v>4616</v>
       </c>
     </row>
-    <row r="4740" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4740" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C4740" s="3"/>
       <c r="D4740" s="3" t="s">
         <v>4617</v>
       </c>
     </row>
-    <row r="4741" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4741" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C4741" s="3"/>
       <c r="D4741" s="3" t="s">
         <v>4618</v>
       </c>
     </row>
-    <row r="4742" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4742" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C4742" s="3"/>
       <c r="D4742" s="3" t="s">
         <v>4619</v>
       </c>
     </row>
-    <row r="4743" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4743" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C4743" s="3"/>
       <c r="D4743" s="3" t="s">
         <v>4620</v>
       </c>
     </row>
-    <row r="4744" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4744" s="2" t="s">
+    <row r="4744" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4744" s="3"/>
+      <c r="D4744" s="3" t="s">
+        <v>4622</v>
+      </c>
+    </row>
+    <row r="4745" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4745" s="3"/>
+      <c r="D4745" s="3" t="s">
+        <v>4621</v>
+      </c>
+    </row>
+    <row r="4746" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4746" s="3"/>
+      <c r="D4746" s="7" t="s">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="4747" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4747" s="3"/>
+      <c r="D4747" s="7" t="s">
+        <v>4623</v>
+      </c>
+    </row>
+    <row r="4748" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4748" s="3"/>
+      <c r="D4748" s="2" t="s">
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="4749" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4749" s="3"/>
+      <c r="D4749" s="2" t="s">
+        <v>4626</v>
+      </c>
+    </row>
+    <row r="4750" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4750" s="3"/>
+      <c r="D4750" s="2" t="s">
+        <v>4627</v>
+      </c>
+    </row>
+    <row r="4751" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4751" s="3" t="s">
+        <v>4629</v>
+      </c>
+      <c r="D4751" s="2"/>
+    </row>
+    <row r="4752" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C4752" s="3"/>
+      <c r="D4752" s="2" t="s">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="4753" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C4753" s="3"/>
+      <c r="D4753" s="2" t="s">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="4754" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C4754" s="3"/>
+      <c r="D4754" s="2" t="s">
+        <v>4631</v>
+      </c>
+    </row>
+    <row r="4755" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C4755" s="3" t="s">
+        <v>4632</v>
+      </c>
+      <c r="D4755" s="2"/>
+    </row>
+    <row r="4756" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C4756" s="3"/>
+      <c r="D4756" s="3" t="s">
+        <v>4633</v>
+      </c>
+    </row>
+    <row r="4757" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4757" s="2" t="s">
         <v>4566</v>
       </c>
     </row>
-    <row r="4745" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4745" s="3"/>
-      <c r="C4745" s="3" t="s">
+    <row r="4758" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4758" s="3"/>
+      <c r="C4758" s="3" t="s">
         <v>4567</v>
       </c>
     </row>
-    <row r="4746" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4746" s="3"/>
-      <c r="C4746" s="3" t="s">
+    <row r="4759" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4759" s="3"/>
+      <c r="C4759" s="3" t="s">
         <v>4571</v>
       </c>
     </row>
-    <row r="4747" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4747" s="3"/>
-      <c r="C4747" s="3" t="s">
+    <row r="4760" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4760" s="3"/>
+      <c r="C4760" s="3" t="s">
         <v>4579</v>
       </c>
     </row>
-    <row r="4748" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4748" s="3"/>
-      <c r="C4748" s="3" t="s">
+    <row r="4761" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4761" s="3"/>
+      <c r="C4761" s="3" t="s">
         <v>4580</v>
       </c>
     </row>
-    <row r="4749" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C4749" s="3" t="s">
+    <row r="4762" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C4762" s="3" t="s">
         <v>4581</v>
       </c>
     </row>
-    <row r="4750" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C4750" s="3" t="s">
+    <row r="4763" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C4763" s="3" t="s">
         <v>4583</v>
       </c>
     </row>
